--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260825.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260825.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>400,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1751,6 +1751,24 @@
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>RP_NTD</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>RP</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>5,737,461,838</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
